--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -600,7 +600,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
